--- a/conceptmaps-datatypes-part3/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/conceptmaps-datatypes-part3/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T10:20:46+00:00</t>
+    <t>2026-04-30T10:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
